--- a/artfynd/A 60212-2022 artfynd.xlsx
+++ b/artfynd/A 60212-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60212-2022 artfynd.xlsx
+++ b/artfynd/A 60212-2022 artfynd.xlsx
@@ -1554,7 +1554,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">

--- a/artfynd/A 60212-2022 artfynd.xlsx
+++ b/artfynd/A 60212-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1917,6 +1917,261 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123420406</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57497</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hedstaberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>604311</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6846596</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Forsa</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>2024_2707</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>07:46</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>07:46</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Liam Martin</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123434965</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100545</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hedstaberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>604192</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6846682</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Forsa</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>2024_2816</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Linnéa Kjellberg, Liam Martin</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60212-2022 artfynd.xlsx
+++ b/artfynd/A 60212-2022 artfynd.xlsx
@@ -1919,10 +1919,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123420406</v>
+        <v>123434965</v>
       </c>
       <c r="B12" t="n">
-        <v>57497</v>
+        <v>100545</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1931,25 +1931,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>222771</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1957,16 +1957,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hedstaberget, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>604311</v>
+        <v>604192</v>
       </c>
       <c r="R12" t="n">
-        <v>6846596</v>
+        <v>6846682</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1993,7 +1998,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_2707</t>
+          <t>2024_2816</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2003,7 +2008,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2013,7 +2018,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2033,7 +2038,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Liam Martin</t>
+          <t>Linnéa Kjellberg, Liam Martin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2044,10 +2049,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123434965</v>
+        <v>123420406</v>
       </c>
       <c r="B13" t="n">
-        <v>100545</v>
+        <v>57497</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2056,25 +2061,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222771</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2082,21 +2087,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hedstaberget, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>604192</v>
+        <v>604311</v>
       </c>
       <c r="R13" t="n">
-        <v>6846682</v>
+        <v>6846596</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_2816</t>
+          <t>2024_2707</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg, Liam Martin</t>
+          <t>Liam Martin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">

--- a/artfynd/A 60212-2022 artfynd.xlsx
+++ b/artfynd/A 60212-2022 artfynd.xlsx
@@ -1922,7 +1922,7 @@
         <v>123434965</v>
       </c>
       <c r="B12" t="n">
-        <v>100545</v>
+        <v>100551</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 60212-2022 artfynd.xlsx
+++ b/artfynd/A 60212-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1919,10 +1919,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123434965</v>
+        <v>123420406</v>
       </c>
       <c r="B12" t="n">
-        <v>100554</v>
+        <v>57503</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1931,25 +1931,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222771</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1957,21 +1957,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hedstaberget, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>604192</v>
+        <v>604311</v>
       </c>
       <c r="R12" t="n">
-        <v>6846682</v>
+        <v>6846596</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1998,7 +1993,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_2816</t>
+          <t>2024_2707</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2008,7 +2003,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2018,7 +2013,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2038,7 +2033,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg, Liam Martin</t>
+          <t>Liam Martin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2049,10 +2044,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123420406</v>
+        <v>123434965</v>
       </c>
       <c r="B13" t="n">
-        <v>57497</v>
+        <v>100571</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2061,25 +2056,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>222771</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2087,16 +2082,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hedstaberget, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>604311</v>
+        <v>604192</v>
       </c>
       <c r="R13" t="n">
-        <v>6846596</v>
+        <v>6846682</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_2707</t>
+          <t>2024_2816</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Liam Martin</t>
+          <t>Linnéa Kjellberg, Liam Martin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2171,6 +2171,139 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>102185518</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57484</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>102119</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Göktyta</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Jynx torquilla</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>pulli/nyligen flygga ungar</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bäckravin V Hedstaberget, Hedsta, Forsa, Hls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>604199</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6846695</v>
+      </c>
+      <c r="S14" t="n">
+        <v>100</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Forsa</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-07-11</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>05:07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-07-11</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>05:33</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Tiggande unge hördes i norra delen där skogen öppnar upp sig.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Johan Södercrantz</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Johan Södercrantz</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60212-2022 artfynd.xlsx
+++ b/artfynd/A 60212-2022 artfynd.xlsx
@@ -1922,7 +1922,7 @@
         <v>123420406</v>
       </c>
       <c r="B12" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>123434965</v>
       </c>
       <c r="B13" t="n">
-        <v>100571</v>
+        <v>100589</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>102185518</v>
       </c>
       <c r="B14" t="n">
-        <v>57484</v>
+        <v>57487</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 60212-2022 artfynd.xlsx
+++ b/artfynd/A 60212-2022 artfynd.xlsx
@@ -1922,7 +1922,7 @@
         <v>123420406</v>
       </c>
       <c r="B12" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>123434965</v>
       </c>
       <c r="B13" t="n">
-        <v>100589</v>
+        <v>100591</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>102185518</v>
       </c>
       <c r="B14" t="n">
-        <v>57487</v>
+        <v>57488</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 60212-2022 artfynd.xlsx
+++ b/artfynd/A 60212-2022 artfynd.xlsx
@@ -2047,7 +2047,7 @@
         <v>123434965</v>
       </c>
       <c r="B13" t="n">
-        <v>100591</v>
+        <v>100166</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 60212-2022 artfynd.xlsx
+++ b/artfynd/A 60212-2022 artfynd.xlsx
@@ -1919,10 +1919,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123420406</v>
+        <v>123434965</v>
       </c>
       <c r="B12" t="n">
-        <v>57507</v>
+        <v>100166</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1931,25 +1931,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>222771</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1957,16 +1957,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hedstaberget, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>604311</v>
+        <v>604192</v>
       </c>
       <c r="R12" t="n">
-        <v>6846596</v>
+        <v>6846682</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1993,7 +1998,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_2707</t>
+          <t>2024_2816</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2003,7 +2008,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2013,7 +2018,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2033,7 +2038,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Liam Martin</t>
+          <t>Linnéa Kjellberg, Liam Martin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2044,10 +2049,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123434965</v>
+        <v>123420406</v>
       </c>
       <c r="B13" t="n">
-        <v>100166</v>
+        <v>57507</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2056,25 +2061,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222771</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2082,21 +2087,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hedstaberget, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>604192</v>
+        <v>604311</v>
       </c>
       <c r="R13" t="n">
-        <v>6846682</v>
+        <v>6846596</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_2816</t>
+          <t>2024_2707</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg, Liam Martin</t>
+          <t>Liam Martin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">

--- a/artfynd/A 60212-2022 artfynd.xlsx
+++ b/artfynd/A 60212-2022 artfynd.xlsx
@@ -1919,10 +1919,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123434965</v>
+        <v>123420406</v>
       </c>
       <c r="B12" t="n">
-        <v>100166</v>
+        <v>57507</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1931,25 +1931,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222771</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1957,21 +1957,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hedstaberget, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>604192</v>
+        <v>604311</v>
       </c>
       <c r="R12" t="n">
-        <v>6846682</v>
+        <v>6846596</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1998,7 +1993,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_2816</t>
+          <t>2024_2707</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2008,7 +2003,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2018,7 +2013,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2038,7 +2033,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg, Liam Martin</t>
+          <t>Liam Martin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2049,10 +2044,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123420406</v>
+        <v>123434965</v>
       </c>
       <c r="B13" t="n">
-        <v>57507</v>
+        <v>100166</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2061,25 +2056,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>222771</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2087,16 +2082,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hedstaberget, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>604311</v>
+        <v>604192</v>
       </c>
       <c r="R13" t="n">
-        <v>6846596</v>
+        <v>6846682</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_2707</t>
+          <t>2024_2816</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Liam Martin</t>
+          <t>Linnéa Kjellberg, Liam Martin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
